--- a/artfynd/A 27163-2025 artfynd.xlsx
+++ b/artfynd/A 27163-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>97116384</v>
       </c>
       <c r="B2" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>557047.3041314683</v>
+        <v>557047</v>
       </c>
       <c r="R2" t="n">
-        <v>7119736.656247608</v>
+        <v>7119736</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2021-07-07</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-07-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,16 +775,11 @@
         <v>97116382</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>557193.5479260983</v>
+        <v>557193</v>
       </c>
       <c r="R3" t="n">
-        <v>7119874.451857273</v>
+        <v>7119875</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2021-07-07</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-07-07</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
